--- a/scenarios/rs6_public_data/Data/inputs/Model_Parameters.xlsx
+++ b/scenarios/rs6_public_data/Data/inputs/Model_Parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\RDR\scenarios\rs6_public_data\Data\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AEAB0F-95CC-4FB5-B9C3-E80E1B6AF0BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A783EE41-5163-46D6-965F-5DEAB0958D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="7" r:id="rId1"/>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>HazardDim2</t>
-  </si>
-  <si>
-    <t>base</t>
   </si>
   <si>
     <t>haz1</t>
@@ -277,6 +274,9 @@
   </si>
   <si>
     <t>Hypothetical 25% stronger quake than the 2022 Ferndale earthquake, with damage potentially to any bridge</t>
+  </si>
+  <si>
+    <t>standard</t>
   </si>
 </sst>
 </file>
@@ -744,7 +744,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="6" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -770,7 +770,7 @@
     </row>
     <row r="3" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -796,7 +796,7 @@
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -810,7 +810,7 @@
     </row>
     <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -836,7 +836,7 @@
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -850,7 +850,7 @@
     </row>
     <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -876,7 +876,7 @@
     </row>
     <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -890,7 +890,7 @@
     </row>
     <row r="12" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -916,7 +916,7 @@
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -930,7 +930,7 @@
     </row>
     <row r="15" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -956,7 +956,7 @@
     </row>
     <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -970,7 +970,7 @@
     </row>
     <row r="18" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -996,7 +996,7 @@
     </row>
     <row r="20" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="21" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -1259,15 +1259,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
         <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1351,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>0.1</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1371,7 +1371,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>0.05</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>125</v>
@@ -1391,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>0.01</v>
@@ -1440,7 +1440,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
